--- a/resources/userdata/info_database.xlsx
+++ b/resources/userdata/info_database.xlsx
@@ -1091,7 +1091,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>,デジモ,数位马赛克,数码模型,數位模型,數位馬賽克,薄格,シミュレーション,模拟,模擬,</t>
+          <t>,デジモ,数码模型,數位模型,數位馬賽克,薄格,シミュレーション,模拟,模擬,数位马赛克,</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>,ロリ,ロリ系,萝莉,蘿莉,萝莉系,炉利,炉利系,童顔,童颜,</t>
+          <t>,ロリ,ロリ系,口リ,炉利,炉利系,童顔,童颜,萝莉,萝莉系,蘿莉,</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>,偷情·被偷情·NTR,寝取,寝取られ,寝取り·寝取られ·ntr,寝取り·寝取られ·ＮＴＲ,寝取り、寝取られ,寝取り・寝取られ,寝取り・寝取られ・NTR,寝取り･寝取られ,寢取,浮気,不倫・浮気,出轨/NTR,</t>
+          <t>,偷情·被偷情·NTR,寝取,寝取られ,寝取り·寝取られ·ntr,寝取り·寝取られ·ＮＴＲ,寝取り、寝取られ,寝取り・寝取られ,寝取り・寝取られ・NTR,寝取り･寝取られ,寢取,浮気,不倫・浮気,出轨/NTR,白天出轨,出轨,</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>,お婆ちゃん,</t>
+          <t>,お婆ちゃん,婆婆,</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>,デリヘル,デリヘル嬢,外送女郎,外送服务,視訊小姐,</t>
+          <t>,デリヘル,デリヘル嬢,デリ嬢,外送女郎,外送服务,应召女郎,視訊小姐,</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>,キャバ嬢,キャバ嬢・風俗嬢,夜店女郎・風俗女郎,風俗嬢,ストリップ,</t>
+          <t>,キャバ嬢,キャバ嬢・風俗嬢,夜店女郎・風俗女郎,風俗嬢,ストリップ,妓女,</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>,ニューハーフ,人妖,变性人,变性者,變性人,變性者,</t>
+          <t>,オカマ,ニューハーフ,人妖,变性人,变性者,變性人,變性者,</t>
         </is>
       </c>
     </row>
@@ -3335,7 +3335,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>,G罩杯,H罩杯,I罩杯,Gカップ,Hカップ,Iカップ,</t>
+          <t>,G罩杯,H罩杯,I罩杯,Gカップ,Hカップ,Iカップ,超乳,</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>,人妻·主妇,人妻・主婦,人妻主婦,成熟女人 / 已婚女人,熟女/人妻,熟女·人妻,熟女・人妻,</t>
+          <t>,人妻·主妇,人妻・主婦,人妻主婦,成熟女人 / 已婚女人,熟女/人妻,熟女·人妻,熟女・人妻,成熟的女人,</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>,治愈系,治癒系,癒し系,</t>
+          <t>,治愈系,治癒系,癒し系,癒やし系,</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>,アナルセックス,アナルバック,アナルファック,アナル中出し,后入式肛交,肛交,肛交内射,肛內中出,肛内中出,肛内射精,肛射,肛門・肛交,肛門射精,アナル から フェラ,肛交后口交,肛交轉口交,</t>
+          <t>,アナルセックス,アナルバック,アナルファック,アナル中出し,后入式肛交,肛交,肛交内射,肛內中出,肛内中出,肛内射精,肛射,肛門・肛交,肛門射精,アナル から フェラ,肛交后口交,肛交轉口交,肛门・肛交,</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>,大屁股,巨大屁股,巨尻,巨臀,</t>
+          <t>,デカ尻,大屁股,巨大屁股,巨尻,巨臀,</t>
         </is>
       </c>
     </row>
@@ -4875,7 +4875,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>,巨乳フェチ,巨乳控,巨乳癖,愛巨乳,爱巨乳,</t>
+          <t>,巨乳フェチ,巨乳控,巨乳癖,愛巨乳,爱巨乳,恋乳癖,</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>,纖細,苗条,苗条的,苗條,苗條的,スレンダー,</t>
+          <t>,スレンダ,スレンダー,纖細,苗条,苗条的,苗條,苗條的,</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>,ロングヘアー,長髮,长发,</t>
+          <t>,ロングヘア,ロングヘアー,長髮,长发,</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>,ショートヘアー,短髮,短发,ショートカット,短发造型,</t>
+          <t>,ショートカット,ショートヘア,ショートヘアー,短发,短发造型,短髮,</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>,くびれ,纖腰,纤腰,腰線,腰线,</t>
+          <t>,くびれ,クビレ,纖腰,纤腰,腰線,腰线,</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>,お掃除フェラ,フェラ,口交,清洁口交,フェラモノ,口交题材,タマ舐め,舔蛋,舔蛋蛋,</t>
+          <t>,お掃除フェラ,フェラ,口交,清洁口交,フェラモノ,口交题材,タマ舐め,舔蛋,舔蛋蛋,立即口交,</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>,イラマチオ,喉奥,強迫口交,强迫口交,深喉,</t>
+          <t>,イラマ,イラマチオ,喉奥,強迫口交,强迫口交,深喉,</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>,ぽちゃカワ,ぽっちゃり,丰满,丰腴,坦克,大號美女,肉肉女,胖女人,豐滿,豐腴,</t>
+          <t>,ぽちゃ,ぽちゃり,ぽちゃカワ,ぽっちゃり,グラマー,ポッチャリ,丰满,丰腴,坦克,大號美女,肉肉女,胖女人,豐滿,豐腴,</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>,フィスト,拳交,拳头,</t>
+          <t>,フィスト,フィストファク,フィストファック,拳交,拳头,</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>,乳房,素敵なおっぱい,美乳,自然乳房,</t>
+          <t>,乳房,素敵なおっぱい,美乳,美乳り,自然乳房,</t>
         </is>
       </c>
     </row>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>,イメージビデオ,グラビア,介紹影片,介绍影片,写真,写真偶像,写真集,寫真,寫真偶像,形象影片,形象视频,</t>
+          <t>,イメージビデオ,グラドル,グラビア,グラビアアイドル,介紹影片,介绍影片,写真,写真偶像,写真集,寫真,寫真偶像,形象影片,形象视频,</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>,PICKUP素人,业余,業餘,素人,素人作品,配信専用素人,</t>
+          <t>,PICKUP素人,业余,業餘,素人,素人作品,配信専用素人,业余地面商品,</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>,FFM,兩女一男,双飞,雙飛,</t>
+          <t>,FFM,兩女一男,双飞,雙飛,两女一男,</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="D775" t="inlineStr">
         <is>
-          <t>,かわいい,</t>
+          <t>,かわいい,カワイイ,</t>
         </is>
       </c>
     </row>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="D777" t="inlineStr">
         <is>
-          <t>,かわいい系,</t>
+          <t>,かわいい系,カワイイ系,可愛い系,</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17547,7 @@
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>,たれ乳,</t>
+          <t>,たれ乳,垂れ乳,</t>
         </is>
       </c>
     </row>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="D782" t="inlineStr">
         <is>
-          <t>,ちょいぽちゃ,</t>
+          <t>,ちょいぽちゃ,ちょいポチャ,ややぽちゃ,ややぽっちゃ,ややポチャ,ヤヤぽちゃ,ヤヤポチャ,</t>
         </is>
       </c>
     </row>
@@ -17789,7 +17789,7 @@
       </c>
       <c r="D790" t="inlineStr">
         <is>
-          <t>,ぽちゃ巨乳,</t>
+          <t>,ぽちゃ巨乳,ぽっちゃり巨乳,ポチャ巨乳,</t>
         </is>
       </c>
     </row>
@@ -17943,7 +17943,7 @@
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>,むっちり,</t>
+          <t>,むっちり,ムチムチ,ムッチムチ,ムッチリ,</t>
         </is>
       </c>
     </row>
@@ -17987,7 +17987,7 @@
       </c>
       <c r="D799" t="inlineStr">
         <is>
-          <t>,ものまねタレント,</t>
+          <t>,ものまねタレント,モノマネタレント,</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="D803" t="inlineStr">
         <is>
-          <t>,ややムチ,</t>
+          <t>,ややムチ,ややムッチリ,</t>
         </is>
       </c>
     </row>
@@ -18163,7 +18163,7 @@
       </c>
       <c r="D807" t="inlineStr">
         <is>
-          <t>,わき毛,</t>
+          <t>,わき毛,ワキ毛,</t>
         </is>
       </c>
     </row>
@@ -18559,7 +18559,7 @@
       </c>
       <c r="D825" t="inlineStr">
         <is>
-          <t>,イギリス人,</t>
+          <t>,イギリス人,イギリス出身,</t>
         </is>
       </c>
     </row>
@@ -18647,7 +18647,7 @@
       </c>
       <c r="D829" t="inlineStr">
         <is>
-          <t>,イタリア人,</t>
+          <t>,イタリア人,イタリア出身,</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="D839" t="inlineStr">
         <is>
-          <t>,ウクライナ人,</t>
+          <t>,ウクライナ人,ウクライナ出身,</t>
         </is>
       </c>
     </row>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="D853" t="inlineStr">
         <is>
-          <t>,オランダ人,</t>
+          <t>,オランダ人,オランダ出身,</t>
         </is>
       </c>
     </row>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>,クォーター,</t>
+          <t>,クォーター,クオーター,</t>
         </is>
       </c>
     </row>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="D891" t="inlineStr">
         <is>
-          <t>,コロンビア人,</t>
+          <t>,コロンビア人,コロンビア出身,</t>
         </is>
       </c>
     </row>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="D897" t="inlineStr">
         <is>
-          <t>,ショートボブ,</t>
+          <t>,ショートボブ,ショートボブヘアー,</t>
         </is>
       </c>
     </row>
@@ -20781,7 +20781,7 @@
       </c>
       <c r="D926" t="inlineStr">
         <is>
-          <t>,スーパーボディ,</t>
+          <t>,スーパーボディ,スーパーボディー,</t>
         </is>
       </c>
     </row>
@@ -20979,7 +20979,7 @@
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>,ダイナマイトボディ,</t>
+          <t>,ダイナマイトボディ,ダイナマイトボディー,</t>
         </is>
       </c>
     </row>
@@ -21045,7 +21045,7 @@
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>,チェコ人,</t>
+          <t>,チェコ人,チェコ出身,</t>
         </is>
       </c>
     </row>
@@ -21111,7 +21111,7 @@
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>,チャットレディ,</t>
+          <t>,チャットレディ,チャットレディー,</t>
         </is>
       </c>
     </row>
@@ -21221,7 +21221,7 @@
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>,デカビラ,</t>
+          <t>,デカビラ,ビラマン,</t>
         </is>
       </c>
     </row>
@@ -21793,7 +21793,7 @@
       </c>
       <c r="D972" t="inlineStr">
         <is>
-          <t>,ハンガリー人,</t>
+          <t>,ハンガリー人,ハンガリー出身,</t>
         </is>
       </c>
     </row>
@@ -21947,7 +21947,7 @@
       </c>
       <c r="D979" t="inlineStr">
         <is>
-          <t>,パフィニップル,</t>
+          <t>,パフィニップル,パフィー,パフィーニップル,</t>
         </is>
       </c>
     </row>
@@ -22013,7 +22013,7 @@
       </c>
       <c r="D982" t="inlineStr">
         <is>
-          <t>,パーフェクトボディ,</t>
+          <t>,パーフェクトボディ,パーフェクトボディー,</t>
         </is>
       </c>
     </row>
@@ -22475,7 +22475,7 @@
       </c>
       <c r="D1003" t="inlineStr">
         <is>
-          <t>,ブラジル人,</t>
+          <t>,ブラジル人,ブラジル出身,</t>
         </is>
       </c>
     </row>
@@ -23311,7 +23311,7 @@
       </c>
       <c r="D1041" t="inlineStr">
         <is>
-          <t>,ムチムチボディ,</t>
+          <t>,ムチムチボディ,ムッチムチボディ,ムッチリボディ,</t>
         </is>
       </c>
     </row>
@@ -23553,7 +23553,7 @@
       </c>
       <c r="D1052" t="inlineStr">
         <is>
-          <t>,モリマン,</t>
+          <t>,モリマン,剛毛おま○こ,剛毛マンコ,</t>
         </is>
       </c>
     </row>
@@ -23729,7 +23729,7 @@
       </c>
       <c r="D1060" t="inlineStr">
         <is>
-          <t>,ラトビア人,</t>
+          <t>,ラトビア人,ラトビア出身,</t>
         </is>
       </c>
     </row>
@@ -23883,7 +23883,7 @@
       </c>
       <c r="D1067" t="inlineStr">
         <is>
-          <t>,ロケットおっぱい,</t>
+          <t>,ロケットおっぱい,ロケットオッパイ,ロケット乳,</t>
         </is>
       </c>
     </row>
@@ -23971,7 +23971,7 @@
       </c>
       <c r="D1071" t="inlineStr">
         <is>
-          <t>,ロシア人,</t>
+          <t>,ロシア人,ロシア出身,</t>
         </is>
       </c>
     </row>
@@ -24433,7 +24433,7 @@
       </c>
       <c r="D1092" t="inlineStr">
         <is>
-          <t>,剛毛マ○毛,</t>
+          <t>,剛毛マ○毛,剛毛マ〇毛,剛毛マン毛,</t>
         </is>
       </c>
     </row>
@@ -24521,7 +24521,7 @@
       </c>
       <c r="D1096" t="inlineStr">
         <is>
-          <t>,勃起デカチクビ,</t>
+          <t>,勃起デカチクビ,勃起デカ乳首,</t>
         </is>
       </c>
     </row>
@@ -24829,7 +24829,7 @@
       </c>
       <c r="D1110" t="inlineStr">
         <is>
-          <t>,右大腿タトゥー,</t>
+          <t>,右大腿タトゥー,右腿にタトゥー,</t>
         </is>
       </c>
     </row>
@@ -25467,7 +25467,7 @@
       </c>
       <c r="D1139" t="inlineStr">
         <is>
-          <t>,左上腕タトゥー,</t>
+          <t>,左上腕タトゥー,左上腕部タトゥー,</t>
         </is>
       </c>
     </row>
@@ -25731,7 +25731,7 @@
       </c>
       <c r="D1151" t="inlineStr">
         <is>
-          <t>,左大腿タトゥー,</t>
+          <t>,左大腿タトゥー,左大腿部タトゥー,</t>
         </is>
       </c>
     </row>
@@ -27359,7 +27359,7 @@
       </c>
       <c r="D1225" t="inlineStr">
         <is>
-          <t>,背中・腰にタトゥー,</t>
+          <t>,背中・腰にタトゥー,背中腰タトゥー,</t>
         </is>
       </c>
     </row>
@@ -27425,7 +27425,7 @@
       </c>
       <c r="D1228" t="inlineStr">
         <is>
-          <t>,背中左肩タトゥー,</t>
+          <t>,背中左肩タトゥー,背中左肩口にタトゥ,</t>
         </is>
       </c>
     </row>
@@ -27667,7 +27667,7 @@
       </c>
       <c r="D1239" t="inlineStr">
         <is>
-          <t>,腰背面部タトゥー,</t>
+          <t>,腰背面部タトゥー,腰部背面タトゥー,</t>
         </is>
       </c>
     </row>
@@ -27975,7 +27975,7 @@
       </c>
       <c r="D1253" t="inlineStr">
         <is>
-          <t>,陥没ちくび,</t>
+          <t>,陥没ちくび,陥没チクビ,</t>
         </is>
       </c>
     </row>

--- a/resources/userdata/info_database.xlsx
+++ b/resources/userdata/info_database.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1194"/>
+  <dimension ref="A1:D1278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26678,6 +26678,1854 @@
       <c r="D1194" t="inlineStr">
         <is>
           <t>,Ｇカップ,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>10代</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>10代</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>10代</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>,10代,10代,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>3P、4P</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>3P、4P</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>3P、4P</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>,3P、4P,3P、4P,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>3P・4P</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>多P</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>多P</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>,3P・4P,多P,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>Tシャツ</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Tシャツ</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Tシャツ</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>,Tシャツ,Tシャツ,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>Tバック、まんぐり返し</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>丁字裤</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>丁字褲</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>,Tバック、まんぐり返し,丁字裤,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>アナルセックス（男の娘）</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>アナルセックス（男の娘）</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>アナルセックス（男の娘）</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>,アナルセックス（男の娘）,アナルセックス（男の娘）,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>アパート</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>公寓</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>公寓</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>,アパート,公寓,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>エレベーター</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>电梯</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>電梯</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>,エレベーター,电梯,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>カラオケルーム</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>KTV</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>KTV</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>,カラオケルーム,KTV,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>厨房</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>廚房</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>,キッチン,厨房,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>コミック雑誌</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>コミック雑志</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>コミック雑志</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>,コミック雑誌,コミック雑志,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>スマホ専用縦動画</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>スマホ専用縦动画</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>スマホ専用縦動畫</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>,スマホ専用縦動画,スマホ専用縦动画,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>ソファ</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>沙发</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>沙發</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>,ソファ,沙发,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>テーブル</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>桌子</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>桌子</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>,テーブル,桌子,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>デカチン</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>デカチン</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>デカチン</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>,デカチン,デカチン,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>厕所</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>廁所</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>,トイレ,厕所,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>ベッド</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>床</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>牀</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>,ベッド,床,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>ベランダ</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>阳台</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>陽臺</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>,ベランダ,阳台,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>マングリ返し</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>打桩机</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>打樁機</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>,マングリ返し,打桩机,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>一泊</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>住一宿</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>住一宿</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>,一泊,住一宿,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>上司</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>上司</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>上司</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>,上司,上司,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>不倫</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>通奸</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>通姦</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>,不倫,通奸,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>主婦</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>主妇</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>主婦</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>,主婦,主妇,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>人妻</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>已婚妇女</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>已婚婦女</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>,人妻,已婚妇女,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>,住宅,住宅,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>全裸</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>全裸</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>全裸</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>,全裸,全裸,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>公園</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>公园</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>公園</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>,公園,公园,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>公衆便所</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>公共厕所</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>公共廁所</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>,公衆便所,公共厕所,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>出張</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>出差</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>出差</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>,出張,出差,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>別荘</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>别墅</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>別墅</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>,別荘,别墅,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>和室</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>和室</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>和室</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>,和室,和室,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>多人数</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>多人数</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>多人數</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>,多人数,多人数,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>夫婦</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>夫妇</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>夫婦</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>,夫婦,夫妇,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>女上司</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>女上司</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>女上司</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>,女上司,女上司,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>女医</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>女医生</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>女醫生</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>,女医,女医生,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>女捜査官</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>女检察官</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>女檢察官</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>,女捜査官,女检察官,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>妹</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>妹</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>妹</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>,妹,妹,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>学校</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>學校</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>,学校,学校,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>家事</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>做家务</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>做家務</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>,家事,做家务,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>密会</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>密会</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>密會</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>,密会,密会,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>密室</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>密室</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>密室</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>,密室,密室,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>屋上</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>屋顶</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>屋頂</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>,屋上,屋顶,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>巨大クリ</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>大阴蒂</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>大陰蒂</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>,巨大クリ,大阴蒂,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>店長推薦作品</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>推荐作品</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>推薦作品</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>,店長推薦作品,推荐作品,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>掃除</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>吸精</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>吸精</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>,掃除,吸精,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>敏感</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>敏感</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>敏感</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>,敏感,敏感,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>散歩</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>散步</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>散步</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>,散歩,散步,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>新人</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>新人</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>新人</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>,新人,新人,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>新婚夫婦</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>新婚</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>新婚</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>,新婚夫婦,新婚,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>旅行</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>,旅行,旅行,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>昼下がり</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>下午</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>,昼下がり,下午,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>昼間</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>白天</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>,昼間,白天,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>本気泣き</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>眼泪</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>眼淚</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>,本気泣き,眼泪,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>椅子</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>椅子</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>椅子</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>,椅子,椅子,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>母乳</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>母乳</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>母乳</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>,母乳,母乳,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>洋物</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>白人</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>白人</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>,洋物,白人,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>浴衣</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>浴衣</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>浴衣</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>,浴衣,浴衣,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>玄関</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>门口</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>門口</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>,玄関,门口,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>生理中</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>经期</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>經期</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>,生理中,经期,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>畳</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>榻榻米</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>榻榻米</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>,畳,榻榻米,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>着物</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>和服</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>和服</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>,着物,和服,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>睡眠系</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>睡眠系</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>睡眠系</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>,睡眠系,睡眠系,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>破廉恥</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>羞耻</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>羞恥</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>,破廉恥,羞耻,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>秘密</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>秘密</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>祕密</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>,秘密,秘密,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>罵倒</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>骂倒</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>罵倒</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>,罵倒,骂倒,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>美熟女</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>美熟女</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>美熟女</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>,美熟女,美熟女,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>美脚</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>美脚</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>美腳</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>,美脚,美脚,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>羞恥プレイ</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>羞耻プレイ</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>羞恥プレイ</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>,羞恥プレイ,羞耻プレイ,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>脱衣所</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>更衣室</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>更衣室</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>,脱衣所,更衣室,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>自宅</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>家中</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>家中</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>,自宅,家中,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>舌</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>舌头</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>舌頭</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>,舌,舌头,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>街中</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>大街</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>大街</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>,街中,大街,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>複数プレイ</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>乱搞</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>亂搞</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>,複数プレイ,乱搞,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>診察</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>检查</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>檢查</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>,診察,检查,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>車内</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>车内</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>車內</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>,車内,车内,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>部屋</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>房间</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>房間</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>,部屋,房间,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>酒</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>喝酒</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>喝酒</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>,酒,喝酒,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>開口具（ボールギャグ含）</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>开口器</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>開口器</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>,開口具（ボールギャグ含）,开口器,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>階段</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>楼梯</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>樓梯</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>,階段,楼梯,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>風俗</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>风俗</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>風俗</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>,風俗,风俗,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>風呂</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>洗澡</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>洗澡</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>,風呂,洗澡,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>魔女</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>魔女</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>魔女</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>,魔女,魔女,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>魔法少女</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>魔法少女</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>魔法少女</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>,魔法少女,魔法少女,</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>３P</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>多P</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>多P</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>,３P,多P,</t>
         </is>
       </c>
     </row>

--- a/resources/userdata/info_database.xlsx
+++ b/resources/userdata/info_database.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>,勇者姫ミリア最大50％OFF,勇者姬米莉亚最高50%OFF,勇者姬米莉亞最高50%OFF,</t>
+          <t>,勇者姫ミリア最大50％OFF,勇者姬米莉亚最高50%OFF,勇者姬米莉亞最高50%OFF,2020年代前半（DOD）,AV大好きキャンペーン,GW大感謝祭2022,SODグループ40％オフセール,アウトレット,乳！尻！クビレ！キャンペーン,特典付き・セット商品,</t>
         </is>
       </c>
     </row>

--- a/resources/userdata/info_database.xlsx
+++ b/resources/userdata/info_database.xlsx
@@ -2533,12 +2533,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>伴侣</t>
+          <t>情侣</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>伴侶</t>
+          <t>情侶</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>巨大阳具</t>
+          <t>巨根</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>巨大陽具</t>
+          <t>巨根</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -2995,12 +2995,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>风俗嬢</t>
+          <t>风俗娘</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>風俗嬢</t>
+          <t>風俗娘</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>妈妈友</t>
+          <t>宝妈朋友</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>媽媽友</t>
+          <t>寶媽朋友</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>招待小姐</t>
+          <t>前台小姐</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>招待小姐</t>
+          <t>前臺小姐</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>男优潮吹</t>
+          <t>男性潮吹</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>男優潮吹</t>
+          <t>男性潮吹</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>高中生</t>
+          <t>女高中生</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>高中生</t>
+          <t>女高中生</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4623,12 +4623,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>包臀裙</t>
+          <t>紧身裙</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>包臀裙</t>
+          <t>緊身裙</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>私处近拍</t>
+          <t>局部特写</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>私處近拍</t>
+          <t>局部特寫</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5503,12 +5503,12 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>立即插入</t>
+          <t>即插</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>立即插入</t>
+          <t>即插</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -5586,7 +5586,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>裸体围裙</t>
+          <t>裸エプロン</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5982,7 +5982,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>女体料理</t>
+          <t>女体盛り</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>,女体盛,女体盛り,女體料理,女體盛,</t>
+          <t>,女体盛,女体盛り,女體料理,女體盛,女体料理,</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>侧位</t>
+          <t>侧位中出</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>側位</t>
+          <t>側位中出</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>粪便</t>
+          <t>粪尿</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>糞便</t>
+          <t>糞尿</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>插入手指</t>
+          <t>指交</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>插入手指</t>
+          <t>指交</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>首次亮相</t>
+          <t>出道作品</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>首次亮相</t>
+          <t>出道作品</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>下码</t>
+          <t>首次露背</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>下碼</t>
+          <t>首次露背</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -6999,12 +6999,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>叔母</t>
+          <t>阿姨</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>叔母</t>
+          <t>阿姨</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>经历告白</t>
+          <t>体验告白</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>經歷告白</t>
+          <t>體驗告白</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>着衣色情</t>
+          <t>着衣</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>著衣色情</t>
+          <t>着衣</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>性别转型/女体化</t>
+          <t>女体化</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>性別轉型/女體化</t>
+          <t>女體化</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>故意露胸</t>
+          <t>露胸</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>故意露胸</t>
+          <t>露胸</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>游戏改</t>
+          <t>游戏真人版</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>遊戲改</t>
+          <t>遊戲真人版</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>原作改编</t>
+          <t>原作联动</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>原作改編</t>
+          <t>原作聯動</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>早泄</t>
+          <t>速射</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>早泄</t>
+          <t>速射</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>中出乞求</t>
+          <t>求中出</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>中出乞求</t>
+          <t>求中出</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -8363,12 +8363,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>子宫颈</t>
+          <t>子宫口</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>子宮頸</t>
+          <t>子宮口</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -8671,12 +8671,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>礼仪小姐</t>
+          <t>陪酒女郎</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>禮儀小姐</t>
+          <t>陪酒女郎</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>历史剧</t>
+          <t>古装剧</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>歷史劇</t>
+          <t>古裝劇</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -12015,12 +12015,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>素人接触</t>
+          <t>素人搭讪</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>素人接觸</t>
+          <t>素人搭訕</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -13269,12 +13269,12 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>这就是！素人</t>
+          <t>这才叫素人</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>這就是！素人</t>
+          <t>這才叫素人</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -14171,12 +14171,12 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>马上就射</t>
+          <t>速射</t>
         </is>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>馬上就射</t>
+          <t>速射</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -15310,14 +15310,14 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
+          <t>ブラックドッグ/妄想族</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
           <t>征服/妄想族</t>
         </is>
       </c>
-      <c r="B678" t="inlineStr">
-        <is>
-          <t>征服/妄想族</t>
-        </is>
-      </c>
       <c r="C678" t="inlineStr">
         <is>
           <t>徵服/妄想族</t>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>,ブラックドッグ/妄想族,</t>
+          <t>,ブラックドッグ/妄想族,征服/妄想族,</t>
         </is>
       </c>
     </row>
@@ -17339,12 +17339,12 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>姐姐系</t>
+          <t>御姐系</t>
         </is>
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>姐姐系</t>
+          <t>御姐系</t>
         </is>
       </c>
       <c r="D770" t="inlineStr">
@@ -17383,12 +17383,12 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>点心系偶像</t>
+          <t>糖果系偶像</t>
         </is>
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>點心系偶像</t>
+          <t>糖果系偶像</t>
         </is>
       </c>
       <c r="D772" t="inlineStr">
@@ -17493,12 +17493,12 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>白人交合</t>
+          <t>白人做爱</t>
         </is>
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>白人交合</t>
+          <t>白人做愛</t>
         </is>
       </c>
       <c r="D777" t="inlineStr">
@@ -18725,12 +18725,12 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>色色乳</t>
+          <t>色乳</t>
         </is>
       </c>
       <c r="C833" t="inlineStr">
         <is>
-          <t>色色乳</t>
+          <t>色乳</t>
         </is>
       </c>
       <c r="D833" t="inlineStr">
@@ -18747,12 +18747,12 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>色色乳房</t>
+          <t>色乳房</t>
         </is>
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>色色乳房</t>
+          <t>色乳房</t>
         </is>
       </c>
       <c r="D834" t="inlineStr">
@@ -18769,12 +18769,12 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>色色乳晕</t>
+          <t>色乳晕</t>
         </is>
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>色色乳暈</t>
+          <t>色乳暈</t>
         </is>
       </c>
       <c r="D835" t="inlineStr">
@@ -18791,12 +18791,12 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>色色乳头</t>
+          <t>色乳头</t>
         </is>
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>色色乳頭</t>
+          <t>色乳頭</t>
         </is>
       </c>
       <c r="D836" t="inlineStr">
@@ -19077,12 +19077,12 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>货真价实的素人姑娘</t>
+          <t>真素人姑娘</t>
         </is>
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>貨真價實的素人姑娘</t>
+          <t>真素人姑娘</t>
         </is>
       </c>
       <c r="D849" t="inlineStr">
@@ -20969,12 +20969,12 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>高腰泳装</t>
+          <t>高叉泳装</t>
         </is>
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>高腰泳裝</t>
+          <t>高叉泳裝</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
@@ -21321,12 +21321,12 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>塑料皮写真</t>
+          <t>塑封写真</t>
         </is>
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>塑料皮寫真</t>
+          <t>塑封寫真</t>
         </is>
       </c>
       <c r="D951" t="inlineStr">
@@ -25721,12 +25721,12 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>厚实阴部</t>
+          <t>厚肉鲍鱼</t>
         </is>
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>厚實陰部</t>
+          <t>厚肉鮑魚</t>
         </is>
       </c>
       <c r="D1151" t="inlineStr">
@@ -26689,12 +26689,12 @@
       </c>
       <c r="B1195" t="inlineStr">
         <is>
-          <t>10代</t>
+          <t>十几岁</t>
         </is>
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>10代</t>
+          <t>十幾歲</t>
         </is>
       </c>
       <c r="D1195" t="inlineStr">
@@ -26755,12 +26755,12 @@
       </c>
       <c r="B1198" t="inlineStr">
         <is>
-          <t>Tシャツ</t>
+          <t>T恤</t>
         </is>
       </c>
       <c r="C1198" t="inlineStr">
         <is>
-          <t>Tシャツ</t>
+          <t>T恤</t>
         </is>
       </c>
       <c r="D1198" t="inlineStr">
@@ -26777,12 +26777,12 @@
       </c>
       <c r="B1199" t="inlineStr">
         <is>
-          <t>丁字裤</t>
+          <t>丁字裤、大开腿</t>
         </is>
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>丁字褲</t>
+          <t>丁字褲、大開腿</t>
         </is>
       </c>
       <c r="D1199" t="inlineStr">
@@ -26799,12 +26799,12 @@
       </c>
       <c r="B1200" t="inlineStr">
         <is>
-          <t>アナルセックス（男の娘）</t>
+          <t>肛交（伪娘）</t>
         </is>
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>アナルセックス（男の娘）</t>
+          <t>肛交（僞娘）</t>
         </is>
       </c>
       <c r="D1200" t="inlineStr">
@@ -26909,12 +26909,12 @@
       </c>
       <c r="B1205" t="inlineStr">
         <is>
-          <t>コミック雑志</t>
+          <t>漫画杂志</t>
         </is>
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>コミック雑志</t>
+          <t>漫畫雜誌</t>
         </is>
       </c>
       <c r="D1205" t="inlineStr">
@@ -26931,12 +26931,12 @@
       </c>
       <c r="B1206" t="inlineStr">
         <is>
-          <t>スマホ専用縦动画</t>
+          <t>手机专用竖屏视频</t>
         </is>
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>スマホ専用縦動畫</t>
+          <t>手機專用豎屏視頻</t>
         </is>
       </c>
       <c r="D1206" t="inlineStr">
@@ -26997,12 +26997,12 @@
       </c>
       <c r="B1209" t="inlineStr">
         <is>
-          <t>デカチン</t>
+          <t>巨屌</t>
         </is>
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>デカチン</t>
+          <t>巨屌</t>
         </is>
       </c>
       <c r="D1209" t="inlineStr">
@@ -27151,12 +27151,12 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>通奸</t>
+          <t>婚外情</t>
         </is>
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>通姦</t>
+          <t>婚外情</t>
         </is>
       </c>
       <c r="D1216" t="inlineStr">
@@ -27195,12 +27195,12 @@
       </c>
       <c r="B1218" t="inlineStr">
         <is>
-          <t>已婚妇女</t>
+          <t>人妻</t>
         </is>
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>已婚婦女</t>
+          <t>人妻</t>
         </is>
       </c>
       <c r="D1218" t="inlineStr">
@@ -27459,12 +27459,12 @@
       </c>
       <c r="B1230" t="inlineStr">
         <is>
-          <t>女检察官</t>
+          <t>女搜查官</t>
         </is>
       </c>
       <c r="C1230" t="inlineStr">
         <is>
-          <t>女檢察官</t>
+          <t>女搜查官</t>
         </is>
       </c>
       <c r="D1230" t="inlineStr">
@@ -27635,12 +27635,12 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>推荐作品</t>
+          <t>店长推荐作品</t>
         </is>
       </c>
       <c r="C1238" t="inlineStr">
         <is>
-          <t>推薦作品</t>
+          <t>店長推薦作品</t>
         </is>
       </c>
       <c r="D1238" t="inlineStr">
@@ -27833,12 +27833,12 @@
       </c>
       <c r="B1247" t="inlineStr">
         <is>
-          <t>眼泪</t>
+          <t>真哭</t>
         </is>
       </c>
       <c r="C1247" t="inlineStr">
         <is>
-          <t>眼淚</t>
+          <t>真哭</t>
         </is>
       </c>
       <c r="D1247" t="inlineStr">
@@ -28097,12 +28097,12 @@
       </c>
       <c r="B1259" t="inlineStr">
         <is>
-          <t>骂倒</t>
+          <t>辱骂</t>
         </is>
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>罵倒</t>
+          <t>辱罵</t>
         </is>
       </c>
       <c r="D1259" t="inlineStr">
@@ -28163,12 +28163,12 @@
       </c>
       <c r="B1262" t="inlineStr">
         <is>
-          <t>羞耻プレイ</t>
+          <t>羞耻play</t>
         </is>
       </c>
       <c r="C1262" t="inlineStr">
         <is>
-          <t>羞恥プレイ</t>
+          <t>羞恥play</t>
         </is>
       </c>
       <c r="D1262" t="inlineStr">
@@ -28273,12 +28273,12 @@
       </c>
       <c r="B1267" t="inlineStr">
         <is>
-          <t>乱搞</t>
+          <t>多人玩法</t>
         </is>
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>亂搞</t>
+          <t>多人玩法</t>
         </is>
       </c>
       <c r="D1267" t="inlineStr">

--- a/resources/userdata/info_database.xlsx
+++ b/resources/userdata/info_database.xlsx
@@ -1912,7 +1912,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>动画角色</t>
+          <t>アニメキャラクター</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6576,14 +6576,14 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
+          <t>その他ファッション</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
           <t>其他服饰</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>其他服饰</t>
-        </is>
-      </c>
       <c r="C281" t="inlineStr">
         <is>
           <t>其他服飾</t>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>,男装,マイクロビキニ,極小比基尼,超小比基尼,サングラス,太阳镜,太陽鏡,ジーンズ,牛仔裤,牛仔褲,スーツ,套裝,西装,セーター,毛衣,タンクトップ,背心,パジャマ,睡衣,ハットタイプ,帽型,ハイヒール,高跟鞋,リボン,絲帶,蝴蝶结,蒙面男（含面具）,覆面男（マスク含）,面具男,休閒裝,便服,普段着,コート,大衣,</t>
+          <t>,男装,マイクロビキニ,極小比基尼,超小比基尼,サングラス,太阳镜,太陽鏡,ジーンズ,牛仔裤,牛仔褲,スーツ,套裝,西装,セーター,毛衣,タンクトップ,背心,パジャマ,睡衣,ハットタイプ,帽型,ハイヒール,高跟鞋,リボン,絲帶,蝴蝶结,蒙面男（含面具）,覆面男（マスク含）,面具男,休閒裝,便服,普段着,コート,大衣,其他服饰,</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>成人动画</t>
+          <t>アダルトアニメ</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8820,14 +8820,14 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
+          <t>キャンギャル</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
           <t>展场女郎</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>展场女郎</t>
-        </is>
-      </c>
       <c r="C383" t="inlineStr">
         <is>
           <t>展場女郎</t>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>,Show Girl,campaign girl,キャンギャル,促销女郎,宣传女郎,宣傳女郎,展场女孩,展場女孩,展場女郎,活动女郎,活動女郎,车模,</t>
+          <t>,Show Girl,campaign girl,キャンギャル,促销女郎,宣传女郎,宣傳女郎,展场女孩,展場女孩,展場女郎,活动女郎,活動女郎,车模,展场女郎,</t>
         </is>
       </c>
     </row>
@@ -10030,14 +10030,14 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
+          <t>熟女はつらいよ</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
           <t>熟女不好当</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>熟女不好当</t>
-        </is>
-      </c>
       <c r="C438" t="inlineStr">
         <is>
           <t>熟女不好當</t>
@@ -10045,7 +10045,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>,熟女はつらいよ,熟女はつらいよ/熟女卍,</t>
+          <t>,熟女はつらいよ,熟女はつらいよ/熟女卍,熟女不好当,</t>
         </is>
       </c>
     </row>
@@ -11306,14 +11306,14 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
+          <t>山と空/妄想族</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
           <t>山与空/妄想族</t>
         </is>
       </c>
-      <c r="B496" t="inlineStr">
-        <is>
-          <t>山与空/妄想族</t>
-        </is>
-      </c>
       <c r="C496" t="inlineStr">
         <is>
           <t>山與空/妄想族</t>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>,山と空/妄想族,</t>
+          <t>,山と空/妄想族,山与空/妄想族,</t>
         </is>
       </c>
     </row>
@@ -12406,14 +12406,14 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
+          <t>人妻花園劇場</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
           <t>人妻花园剧场</t>
         </is>
       </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>人妻花园剧场</t>
-        </is>
-      </c>
       <c r="C546" t="inlineStr">
         <is>
           <t>人妻花園劇場</t>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>,人妻花園劇場,</t>
+          <t>,人妻花園劇場,人妻花园剧场,</t>
         </is>
       </c>
     </row>
@@ -13660,14 +13660,14 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
+          <t>人妻援護会/エマニエル</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
           <t>人妻后援会</t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
-        <is>
-          <t>人妻后援会</t>
-        </is>
-      </c>
       <c r="C603" t="inlineStr">
         <is>
           <t>人妻後援會</t>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>,人妻援護会/エマニエル,</t>
+          <t>,人妻援護会/エマニエル,人妻后援会,</t>
         </is>
       </c>
     </row>
@@ -14540,22 +14540,22 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
+          <t>ボニータ/妄想族</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
           <t>美女/妄想族</t>
         </is>
       </c>
-      <c r="B643" t="inlineStr">
+      <c r="C643" t="inlineStr">
         <is>
           <t>美女/妄想族</t>
         </is>
       </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>美女/妄想族</t>
-        </is>
-      </c>
       <c r="D643" t="inlineStr">
         <is>
-          <t>,ボニータ/妄想族,</t>
+          <t>,ボニータ/妄想族,美女/妄想族,</t>
         </is>
       </c>
     </row>
@@ -15596,14 +15596,14 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
+          <t>痴ロモン/妄想族</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
           <t>痴兽/妄想族</t>
         </is>
       </c>
-      <c r="B691" t="inlineStr">
-        <is>
-          <t>痴兽/妄想族</t>
-        </is>
-      </c>
       <c r="C691" t="inlineStr">
         <is>
           <t>癡獸/妄想族</t>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>,痴ロモン/妄想族,</t>
+          <t>,痴ロモン/妄想族,痴兽/妄想族,</t>
         </is>
       </c>
     </row>
@@ -16982,14 +16982,14 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
+          <t>新宿交縁女子</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
           <t>新宿约会女孩</t>
         </is>
       </c>
-      <c r="B754" t="inlineStr">
-        <is>
-          <t>新宿约会女孩</t>
-        </is>
-      </c>
       <c r="C754" t="inlineStr">
         <is>
           <t>新宿約會女孩</t>
@@ -16997,7 +16997,7 @@
       </c>
       <c r="D754" t="inlineStr">
         <is>
-          <t>,新宿交縁女子,</t>
+          <t>,新宿交縁女子,新宿约会女孩,</t>
         </is>
       </c>
     </row>

--- a/resources/userdata/info_database.xlsx
+++ b/resources/userdata/info_database.xlsx
@@ -5403,7 +5403,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>群交</t>
+          <t>羣交</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -16007,7 +16007,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>禁欲者的餐桌/妄想族</t>
+          <t>禁慾者的餐桌/妄想族</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="C1982" t="inlineStr">
         <is>
-          <t>第一次的「真傢伙」生屌</t>
+          <t>第一次的「真傢夥」生屌</t>
         </is>
       </c>
       <c r="D1982" t="inlineStr">
@@ -51510,7 +51510,7 @@
       </c>
       <c r="B2323" t="inlineStr">
         <is>
-          <t>熟母（长瀬风）</t>
+          <t>熟母（长濑风）</t>
         </is>
       </c>
       <c r="C2323" t="inlineStr">
@@ -64891,7 +64891,7 @@
       </c>
       <c r="C2931" t="inlineStr">
         <is>
-          <t>布里莊園庵</t>
+          <t>布裏莊園庵</t>
         </is>
       </c>
       <c r="D2931" t="inlineStr">
@@ -65375,7 +65375,7 @@
       </c>
       <c r="C2953" t="inlineStr">
         <is>
-          <t>生痴漢</t>
+          <t>生癡漢</t>
         </is>
       </c>
       <c r="D2953" t="inlineStr">
@@ -66167,7 +66167,7 @@
       </c>
       <c r="C2989" t="inlineStr">
         <is>
-          <t>吃媽媽友無限循環</t>
+          <t>喫媽媽友無限循環</t>
         </is>
       </c>
       <c r="D2989" t="inlineStr">
@@ -68301,7 +68301,7 @@
       </c>
       <c r="C3086" t="inlineStr">
         <is>
-          <t>獨占素人</t>
+          <t>獨佔素人</t>
         </is>
       </c>
       <c r="D3086" t="inlineStr">
@@ -68345,7 +68345,7 @@
       </c>
       <c r="C3088" t="inlineStr">
         <is>
-          <t>痴人</t>
+          <t>癡人</t>
         </is>
       </c>
       <c r="D3088" t="inlineStr">
@@ -69264,7 +69264,7 @@
       </c>
       <c r="B3130" t="inlineStr">
         <is>
-          <t>蜃気楼</t>
+          <t>蜃气楼</t>
         </is>
       </c>
       <c r="C3130" t="inlineStr">
@@ -69577,7 +69577,7 @@
       </c>
       <c r="C3144" t="inlineStr">
         <is>
-          <t>靖云會</t>
+          <t>靖雲會</t>
         </is>
       </c>
       <c r="D3144" t="inlineStr">
@@ -69599,7 +69599,7 @@
       </c>
       <c r="C3145" t="inlineStr">
         <is>
-          <t>靖云會極限</t>
+          <t>靖雲會極限</t>
         </is>
       </c>
       <c r="D3145" t="inlineStr">
